--- a/research/traditional_assets/database/data/indonesia/indonesia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.030645</v>
+        <v>0.0241</v>
       </c>
       <c r="E2">
-        <v>-0.0516</v>
+        <v>-0.02300000000000001</v>
       </c>
       <c r="G2">
-        <v>0.08749322394556501</v>
+        <v>0.1005994112485958</v>
       </c>
       <c r="H2">
-        <v>0.08749322394556501</v>
+        <v>0.1005994112485958</v>
       </c>
       <c r="I2">
-        <v>0.08475731611608696</v>
+        <v>0.05706255688666945</v>
       </c>
       <c r="J2">
-        <v>0.08099498599023615</v>
+        <v>0.04575012944470441</v>
       </c>
       <c r="K2">
-        <v>71.15299999999999</v>
+        <v>35.486</v>
       </c>
       <c r="L2">
-        <v>0.02878427469922409</v>
+        <v>0.01454904758390527</v>
       </c>
       <c r="M2">
-        <v>10.3</v>
+        <v>16.71</v>
       </c>
       <c r="N2">
-        <v>0.001857194374323837</v>
+        <v>0.003153264506243312</v>
       </c>
       <c r="O2">
-        <v>0.1447584782089301</v>
+        <v>0.4708899284224765</v>
       </c>
       <c r="P2">
-        <v>10.3</v>
+        <v>16.4</v>
       </c>
       <c r="Q2">
-        <v>0.001857194374323837</v>
+        <v>0.003094765882848015</v>
       </c>
       <c r="R2">
-        <v>0.1447584782089301</v>
+        <v>0.462154088936482</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.3099999999999987</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.0185517654099341</v>
       </c>
       <c r="U2">
-        <v>1062.67</v>
+        <v>523.3099999999999</v>
       </c>
       <c r="V2">
-        <v>0.1916101694915254</v>
+        <v>0.09875133744836551</v>
       </c>
       <c r="W2">
-        <v>0.04432779235928842</v>
+        <v>0.01417978737150253</v>
       </c>
       <c r="X2">
-        <v>0.05766032834662953</v>
+        <v>0.09544080035622823</v>
       </c>
       <c r="Y2">
-        <v>-0.0133325359873411</v>
+        <v>-0.08126101298472571</v>
       </c>
       <c r="Z2">
-        <v>1.657821829456158</v>
+        <v>2.064529562929783</v>
       </c>
       <c r="AA2">
-        <v>0.08367598684210525</v>
+        <v>0.05412714675460154</v>
       </c>
       <c r="AB2">
-        <v>0.05733220391852815</v>
+        <v>0.09526214628356751</v>
       </c>
       <c r="AC2">
-        <v>0.0263437829235771</v>
+        <v>-0.04227609081224919</v>
       </c>
       <c r="AD2">
-        <v>575.976</v>
+        <v>630.967</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>575.976</v>
+        <v>630.967</v>
       </c>
       <c r="AG2">
-        <v>-486.6940000000001</v>
+        <v>107.657</v>
       </c>
       <c r="AH2">
-        <v>0.09408334825226365</v>
+        <v>0.1063982771683493</v>
       </c>
       <c r="AI2">
-        <v>0.2386756925198573</v>
+        <v>0.2701118646955603</v>
       </c>
       <c r="AJ2">
-        <v>-0.09619777890485377</v>
+        <v>0.01991094016989688</v>
       </c>
       <c r="AK2">
-        <v>-0.3603683251070309</v>
+        <v>0.05939247626524231</v>
       </c>
       <c r="AL2">
-        <v>128.698</v>
+        <v>104.25</v>
       </c>
       <c r="AM2">
-        <v>128.698</v>
+        <v>104.25</v>
       </c>
       <c r="AN2">
-        <v>2.293391095219514</v>
+        <v>3.717956725669974</v>
       </c>
       <c r="AO2">
-        <v>1.6279584764332</v>
+        <v>1.33505035971223</v>
       </c>
       <c r="AP2">
-        <v>-1.937892699863825</v>
+        <v>0.6343660876328755</v>
       </c>
       <c r="AQ2">
-        <v>1.6279584764332</v>
+        <v>1.33505035971223</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Sinar Mas Multiartha Tbk (IDX:SMMA)</t>
+          <t>PT Asuransi Multi Artha Guna Tbk (IDX:AMAG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,118 +722,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.135</v>
+        <v>0.0232</v>
       </c>
       <c r="E3">
-        <v>0.234</v>
+        <v>0.164</v>
       </c>
       <c r="G3">
-        <v>0.08927896527107042</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="H3">
-        <v>0.08927896527107042</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="I3">
-        <v>0.08310586654348465</v>
+        <v>0.1788888888888889</v>
       </c>
       <c r="J3">
-        <v>0.07559573299465416</v>
+        <v>0.1717183006535948</v>
       </c>
       <c r="K3">
-        <v>60.8</v>
+        <v>11.5</v>
       </c>
       <c r="L3">
-        <v>0.02553227228824591</v>
+        <v>0.212962962962963</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>16.71</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1454308093994778</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>1.453043478260869</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>16.4</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.1427328111401218</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>1.426086956521739</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.3099999999999987</v>
+      </c>
+      <c r="T3">
+        <v>0.0185517654099341</v>
       </c>
       <c r="U3">
-        <v>1007.5</v>
+        <v>56.8</v>
       </c>
       <c r="V3">
-        <v>0.1923664413640356</v>
+        <v>0.4943429068755439</v>
       </c>
       <c r="W3">
-        <v>0.04432779235928842</v>
+        <v>0.08998435054773084</v>
       </c>
       <c r="X3">
-        <v>0.060347540057512</v>
+        <v>0.09510532720756382</v>
       </c>
       <c r="Y3">
-        <v>-0.01601974769822358</v>
+        <v>-0.005120976659832979</v>
       </c>
       <c r="Z3">
-        <v>1.786790223039262</v>
+        <v>0.5726405090137858</v>
       </c>
       <c r="AA3">
-        <v>0.1350737166183346</v>
+        <v>0.09833285509325683</v>
       </c>
       <c r="AB3">
-        <v>0.05691864770000619</v>
+        <v>0.09510532720756382</v>
       </c>
       <c r="AC3">
-        <v>0.07815506891832844</v>
+        <v>0.003227527885693013</v>
       </c>
       <c r="AD3">
-        <v>575.3</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>575.3</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-432.2</v>
+        <v>-56.8</v>
       </c>
       <c r="AH3">
-        <v>0.09897293856555472</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.2571517968889683</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.08994422708732208</v>
+        <v>-0.9776247848537003</v>
       </c>
       <c r="AK3">
-        <v>-0.351467837683988</v>
+        <v>-1.124752475247525</v>
       </c>
       <c r="AL3">
-        <v>128.6</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>128.6</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>2.4151973131822</v>
-      </c>
-      <c r="AO3">
-        <v>1.538880248833593</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.814441645675903</v>
-      </c>
-      <c r="AQ3">
-        <v>1.538880248833593</v>
+        <v>-5.514563106796116</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Asuransi Kresna Mitra Tbk (IDX:ASMI)</t>
+          <t>PT Sinar Mas Multiartha Tbk (IDX:SMMA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,28 +850,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0633</v>
+        <v>0.00045</v>
       </c>
       <c r="E4">
-        <v>-0.09539999999999998</v>
+        <v>-0.21</v>
       </c>
       <c r="G4">
-        <v>-0.3359605911330049</v>
+        <v>0.09815457546770508</v>
       </c>
       <c r="H4">
-        <v>-0.3359605911330049</v>
+        <v>0.09815457546770508</v>
       </c>
       <c r="I4">
-        <v>0.1152709359605911</v>
+        <v>0.05730974350292051</v>
       </c>
       <c r="J4">
-        <v>0.1152709359605911</v>
+        <v>0.04281609607410767</v>
       </c>
       <c r="K4">
-        <v>2.45</v>
+        <v>29.4</v>
       </c>
       <c r="L4">
-        <v>0.1206896551724138</v>
+        <v>0.01244391771776856</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -898,73 +895,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.84</v>
+        <v>463.4</v>
       </c>
       <c r="V4">
-        <v>0.01742331288343558</v>
+        <v>0.09060514224264346</v>
       </c>
       <c r="W4">
-        <v>0.08974358974358974</v>
+        <v>0.01983939537080774</v>
       </c>
       <c r="X4">
-        <v>0.05738744260488049</v>
+        <v>0.1010043684688603</v>
       </c>
       <c r="Y4">
-        <v>0.03235614713870925</v>
+        <v>-0.08116497309805258</v>
       </c>
       <c r="Z4">
-        <v>0.7593894957354482</v>
+        <v>2.252906006541495</v>
       </c>
       <c r="AA4">
-        <v>0.08753553793206643</v>
+        <v>0.09646064002201489</v>
       </c>
       <c r="AB4">
-        <v>0.05733381748372429</v>
+        <v>0.09757830178886145</v>
       </c>
       <c r="AC4">
-        <v>0.03020172044834215</v>
+        <v>-0.001117661766846564</v>
       </c>
       <c r="AD4">
-        <v>0.328</v>
+        <v>630.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.328</v>
+        <v>630.4</v>
       </c>
       <c r="AG4">
-        <v>-2.512</v>
+        <v>167</v>
       </c>
       <c r="AH4">
-        <v>0.002008228840125392</v>
+        <v>0.109732110219499</v>
       </c>
       <c r="AI4">
-        <v>0.01060527677185722</v>
+        <v>0.287420781470843</v>
       </c>
       <c r="AJ4">
-        <v>-0.01565226060515428</v>
+        <v>0.03161980497964594</v>
       </c>
       <c r="AK4">
-        <v>-0.08943320991170606</v>
+        <v>0.09653737210243366</v>
       </c>
       <c r="AL4">
-        <v>0.021</v>
+        <v>104.2</v>
       </c>
       <c r="AM4">
-        <v>0.021</v>
+        <v>104.2</v>
       </c>
       <c r="AN4">
-        <v>0.1291338582677165</v>
+        <v>3.818291944276196</v>
       </c>
       <c r="AO4">
-        <v>111.4285714285714</v>
+        <v>1.299424184261037</v>
       </c>
       <c r="AP4">
-        <v>-0.9889763779527559</v>
+        <v>1.011508176862508</v>
       </c>
       <c r="AQ4">
-        <v>111.4285714285714</v>
+        <v>1.299424184261037</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Asuransi Multi Artha Guna Tbk (IDX:AMAG)</t>
+          <t>PT Malacca Trust Wuwungan Insurance Tbk (IDX:MTWI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,115 +981,115 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.00201</v>
-      </c>
-      <c r="E5">
-        <v>-0.0516</v>
+        <v>0.025</v>
       </c>
       <c r="G5">
-        <v>0.198501872659176</v>
+        <v>0.07807807807807808</v>
       </c>
       <c r="H5">
-        <v>0.198501872659176</v>
+        <v>0.07807807807807808</v>
       </c>
       <c r="I5">
-        <v>0.2078651685393259</v>
+        <v>0.02087087087087087</v>
       </c>
       <c r="J5">
-        <v>0.1805144884683619</v>
+        <v>0.01043543543543544</v>
       </c>
       <c r="K5">
-        <v>9.949999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="L5">
-        <v>0.1863295880149813</v>
+        <v>0.01141141141141141</v>
       </c>
       <c r="M5">
-        <v>10.3</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.08758503401360546</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>1.035175879396985</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>10.3</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.08758503401360546</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>1.035175879396985</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>47.6</v>
+        <v>1.57</v>
       </c>
       <c r="V5">
-        <v>0.4047619047619048</v>
+        <v>0.1623578076525336</v>
       </c>
       <c r="W5">
-        <v>0.07246904588492352</v>
+        <v>0.008520179372197309</v>
       </c>
       <c r="X5">
-        <v>0.05733220391852815</v>
+        <v>0.09536763899564042</v>
       </c>
       <c r="Y5">
-        <v>0.01513684196639536</v>
+        <v>-0.08684745962344312</v>
       </c>
       <c r="Z5">
-        <v>0.4635416666666666</v>
+        <v>1.130154420498897</v>
       </c>
       <c r="AA5">
-        <v>0.08367598684210525</v>
+        <v>0.01179365348718819</v>
       </c>
       <c r="AB5">
-        <v>0.05733220391852815</v>
+        <v>0.09522817334484002</v>
       </c>
       <c r="AC5">
-        <v>0.0263437829235771</v>
+        <v>-0.08343451985765182</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="AG5">
-        <v>-47.6</v>
+        <v>-1.517</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.005450992492029208</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.006211180124223601</v>
       </c>
       <c r="AJ5">
-        <v>-0.68</v>
+        <v>-0.1860664785968355</v>
       </c>
       <c r="AK5">
-        <v>-0.6063694267515923</v>
+        <v>-0.2178658624156255</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.2226890756302521</v>
+      </c>
+      <c r="AO5">
+        <v>7.722222222222223</v>
       </c>
       <c r="AP5">
-        <v>-4.033898305084746</v>
+        <v>-6.373949579831933</v>
+      </c>
+      <c r="AQ5">
+        <v>7.722222222222223</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT Malacca Trust Wuwungan Insurance Tbk (IDX:MTWI)</t>
+          <t>PT Asuransi Maximus Graha Persada Tbk (IDX:ASMI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1111,23 +1108,26 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.06370000000000001</v>
+      </c>
       <c r="G6">
-        <v>0.104635761589404</v>
+        <v>0.06</v>
       </c>
       <c r="H6">
-        <v>0.104635761589404</v>
+        <v>0.06</v>
       </c>
       <c r="I6">
-        <v>-0.03228476821192053</v>
+        <v>-0.3810126582278481</v>
       </c>
       <c r="J6">
-        <v>-0.03228476821192053</v>
+        <v>-0.3810126582278481</v>
       </c>
       <c r="K6">
-        <v>-0.617</v>
+        <v>-5.49</v>
       </c>
       <c r="L6">
-        <v>-0.1021523178807947</v>
+        <v>-0.3474683544303798</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1151,201 +1151,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3.18</v>
+        <v>1.54</v>
       </c>
       <c r="V6">
-        <v>0.2484375</v>
+        <v>0.02558139534883721</v>
       </c>
       <c r="W6">
-        <v>-0.0678021978021978</v>
+        <v>-0.1609970674486804</v>
       </c>
       <c r="X6">
-        <v>0.05766032834662953</v>
+        <v>0.09551396171681606</v>
       </c>
       <c r="Y6">
-        <v>-0.1254625261488273</v>
+        <v>-0.2565110291654964</v>
       </c>
       <c r="Z6">
-        <v>0.8779069767441862</v>
+        <v>0.4857204340742107</v>
       </c>
       <c r="AA6">
-        <v>-0.02834302325581396</v>
+        <v>-0.1850656337421992</v>
       </c>
       <c r="AB6">
-        <v>0.05731830253794777</v>
+        <v>0.095296119222295</v>
       </c>
       <c r="AC6">
-        <v>-0.08566132579376173</v>
+        <v>-0.2803617529644942</v>
       </c>
       <c r="AD6">
-        <v>0.153</v>
+        <v>0.514</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.153</v>
+        <v>0.514</v>
       </c>
       <c r="AG6">
-        <v>-3.027</v>
+        <v>-1.026</v>
       </c>
       <c r="AH6">
-        <v>0.01181193545896703</v>
+        <v>0.008465922192575023</v>
       </c>
       <c r="AI6">
-        <v>0.01686322054447261</v>
+        <v>0.01916909077347654</v>
       </c>
       <c r="AJ6">
-        <v>-0.3097308912309424</v>
+        <v>-0.01733869604894041</v>
       </c>
       <c r="AK6">
-        <v>-0.5136602749024266</v>
+        <v>-0.04059507794571496</v>
       </c>
       <c r="AL6">
-        <v>0.022</v>
+        <v>0.032</v>
       </c>
       <c r="AM6">
-        <v>0.022</v>
+        <v>0.032</v>
       </c>
       <c r="AN6">
-        <v>-1.627659574468085</v>
+        <v>-0.08667790893760541</v>
       </c>
       <c r="AO6">
-        <v>-8.863636363636365</v>
+        <v>-188.125</v>
       </c>
       <c r="AP6">
-        <v>32.20212765957447</v>
+        <v>0.1730185497470489</v>
       </c>
       <c r="AQ6">
-        <v>-8.863636363636365</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PT Asuransi Harta Aman Pratama Tbk (IDX:AHAP)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>-0.0955</v>
-      </c>
-      <c r="G7">
-        <v>-0.0673394495412844</v>
-      </c>
-      <c r="H7">
-        <v>-0.0673394495412844</v>
-      </c>
-      <c r="I7">
-        <v>-0.1495412844036697</v>
-      </c>
-      <c r="J7">
-        <v>-0.1495412844036697</v>
-      </c>
-      <c r="K7">
-        <v>-1.43</v>
-      </c>
-      <c r="L7">
-        <v>-0.1311926605504587</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>1.55</v>
-      </c>
-      <c r="V7">
-        <v>0.1019736842105263</v>
-      </c>
-      <c r="W7">
-        <v>-0.1311926605504587</v>
-      </c>
-      <c r="X7">
-        <v>0.05768437048738825</v>
-      </c>
-      <c r="Y7">
-        <v>-0.1888770310378469</v>
-      </c>
-      <c r="Z7">
-        <v>1.142557651991614</v>
-      </c>
-      <c r="AA7">
-        <v>-0.1708595387840671</v>
-      </c>
-      <c r="AB7">
-        <v>0.05734238111681651</v>
-      </c>
-      <c r="AC7">
-        <v>-0.2282019199008836</v>
-      </c>
-      <c r="AD7">
-        <v>0.195</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0.195</v>
-      </c>
-      <c r="AG7">
-        <v>-1.355</v>
-      </c>
-      <c r="AH7">
-        <v>0.01266645014615135</v>
-      </c>
-      <c r="AI7">
-        <v>0.01966717095310136</v>
-      </c>
-      <c r="AJ7">
-        <v>-0.0978692668833514</v>
-      </c>
-      <c r="AK7">
-        <v>-0.1619844590555888</v>
-      </c>
-      <c r="AL7">
-        <v>0.055</v>
-      </c>
-      <c r="AM7">
-        <v>0.055</v>
-      </c>
-      <c r="AN7">
-        <v>-0.15</v>
-      </c>
-      <c r="AO7">
-        <v>-29.63636363636363</v>
-      </c>
-      <c r="AP7">
-        <v>1.042307692307692</v>
-      </c>
-      <c r="AQ7">
-        <v>-29.63636363636363</v>
+        <v>-188.125</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/indonesia/indonesia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_insurance_general.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0241</v>
+        <v>0.05535</v>
       </c>
       <c r="E2">
-        <v>-0.02300000000000001</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="G2">
-        <v>0.1005994112485958</v>
+        <v>0.1077581982169855</v>
       </c>
       <c r="H2">
-        <v>0.1005994112485958</v>
+        <v>0.1077581982169855</v>
       </c>
       <c r="I2">
-        <v>0.05706255688666945</v>
+        <v>0.1099327459465095</v>
       </c>
       <c r="J2">
-        <v>0.04575012944470441</v>
+        <v>0.09961805053288561</v>
       </c>
       <c r="K2">
-        <v>35.486</v>
+        <v>82.94500000000001</v>
       </c>
       <c r="L2">
-        <v>0.01454904758390527</v>
+        <v>0.04324331369584485</v>
       </c>
       <c r="M2">
-        <v>16.71</v>
+        <v>16.602</v>
       </c>
       <c r="N2">
-        <v>0.003153264506243312</v>
+        <v>0.002704481404857706</v>
       </c>
       <c r="O2">
-        <v>0.4708899284224765</v>
+        <v>0.2001567303634939</v>
       </c>
       <c r="P2">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="Q2">
-        <v>0.003094765882848015</v>
+        <v>0.002704155602977829</v>
       </c>
       <c r="R2">
-        <v>0.462154088936482</v>
+        <v>0.2001326179998794</v>
       </c>
       <c r="S2">
-        <v>0.3099999999999987</v>
+        <v>0.001999999999998892</v>
       </c>
       <c r="T2">
-        <v>0.0185517654099341</v>
+        <v>0.000120467413564564</v>
       </c>
       <c r="U2">
-        <v>523.3099999999999</v>
+        <v>1029.66</v>
       </c>
       <c r="V2">
-        <v>0.09875133744836551</v>
+        <v>0.1677325818169971</v>
       </c>
       <c r="W2">
-        <v>0.01417978737150253</v>
+        <v>0.07093581599883658</v>
       </c>
       <c r="X2">
-        <v>0.09544080035622823</v>
+        <v>0.08497669874462987</v>
       </c>
       <c r="Y2">
-        <v>-0.08126101298472571</v>
+        <v>-0.01404088274579329</v>
       </c>
       <c r="Z2">
-        <v>2.064529562929783</v>
+        <v>3.034171404346327</v>
       </c>
       <c r="AA2">
-        <v>0.05412714675460154</v>
+        <v>0.1414562527296581</v>
       </c>
       <c r="AB2">
-        <v>0.09526214628356751</v>
+        <v>0.08481960448889225</v>
       </c>
       <c r="AC2">
-        <v>-0.04227609081224919</v>
+        <v>0.0566864369016012</v>
       </c>
       <c r="AD2">
-        <v>630.967</v>
+        <v>786.732</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>630.967</v>
+        <v>786.732</v>
       </c>
       <c r="AG2">
-        <v>107.657</v>
+        <v>-242.9279999999999</v>
       </c>
       <c r="AH2">
-        <v>0.1063982771683493</v>
+        <v>0.1136004223274447</v>
       </c>
       <c r="AI2">
-        <v>0.2701118646955603</v>
+        <v>0.3079629473051305</v>
       </c>
       <c r="AJ2">
-        <v>0.01991094016989688</v>
+        <v>-0.04120376432467197</v>
       </c>
       <c r="AK2">
-        <v>0.05939247626524231</v>
+        <v>-0.15929997403231</v>
       </c>
       <c r="AL2">
-        <v>104.25</v>
+        <v>95.53700000000001</v>
       </c>
       <c r="AM2">
-        <v>104.25</v>
+        <v>95.53700000000001</v>
       </c>
       <c r="AN2">
-        <v>3.717956725669974</v>
+        <v>3.208243958535531</v>
       </c>
       <c r="AO2">
-        <v>1.33505035971223</v>
+        <v>2.207123941509572</v>
       </c>
       <c r="AP2">
-        <v>0.6343660876328755</v>
+        <v>-0.9906452112779437</v>
       </c>
       <c r="AQ2">
-        <v>1.33505035971223</v>
+        <v>2.207123941509572</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Asuransi Multi Artha Guna Tbk (IDX:AMAG)</t>
+          <t>PT Sinar Mas Multiartha Tbk (IDX:SMMA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,115 +722,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0232</v>
+        <v>-0.0742</v>
       </c>
       <c r="E3">
-        <v>0.164</v>
+        <v>-0.0418</v>
       </c>
       <c r="G3">
-        <v>0.2222222222222222</v>
+        <v>0.111330265176419</v>
       </c>
       <c r="H3">
-        <v>0.2222222222222222</v>
+        <v>0.111330265176419</v>
       </c>
       <c r="I3">
-        <v>0.1788888888888889</v>
+        <v>0.1099605522682446</v>
       </c>
       <c r="J3">
-        <v>0.1717183006535948</v>
+        <v>0.08295648736936329</v>
       </c>
       <c r="K3">
-        <v>11.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="L3">
-        <v>0.212962962962963</v>
+        <v>0.04021477098400175</v>
       </c>
       <c r="M3">
-        <v>16.71</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1454308093994778</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>1.453043478260869</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>16.4</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1427328111401218</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.426086956521739</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0.3099999999999987</v>
-      </c>
-      <c r="T3">
-        <v>0.0185517654099341</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>56.8</v>
+        <v>960.8</v>
       </c>
       <c r="V3">
-        <v>0.4943429068755439</v>
+        <v>0.1600933100058319</v>
       </c>
       <c r="W3">
-        <v>0.08998435054773084</v>
+        <v>0.05342066957787482</v>
       </c>
       <c r="X3">
-        <v>0.09510532720756382</v>
+        <v>0.08946576202278003</v>
       </c>
       <c r="Y3">
-        <v>-0.005120976659832979</v>
+        <v>-0.03604509244490521</v>
       </c>
       <c r="Z3">
-        <v>0.5726405090137858</v>
+        <v>3.34881263198839</v>
       </c>
       <c r="AA3">
-        <v>0.09833285509325683</v>
+        <v>0.2778057328079091</v>
       </c>
       <c r="AB3">
-        <v>0.09510532720756382</v>
+        <v>0.08504567278434318</v>
       </c>
       <c r="AC3">
-        <v>0.003227527885693013</v>
+        <v>0.1927600600235659</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>786.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>786.4</v>
       </c>
       <c r="AG3">
-        <v>-56.8</v>
+        <v>-174.4</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.1158532093872921</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.3277076301204317</v>
       </c>
       <c r="AJ3">
-        <v>-0.9776247848537003</v>
+        <v>-0.02992912426421375</v>
       </c>
       <c r="AK3">
-        <v>-1.124752475247525</v>
+        <v>-0.1212036972687469</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>3.357813834329633</v>
+      </c>
+      <c r="AO3">
+        <v>2.101570680628272</v>
       </c>
       <c r="AP3">
-        <v>-5.514563106796116</v>
+        <v>-0.74466268146883</v>
+      </c>
+      <c r="AQ3">
+        <v>2.101570680628272</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Sinar Mas Multiartha Tbk (IDX:SMMA)</t>
+          <t>PT Asuransi Multi Artha Guna Tbk (IDX:AMAG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,118 +853,115 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.00045</v>
+        <v>0.0287</v>
       </c>
       <c r="E4">
-        <v>-0.21</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="G4">
-        <v>0.09815457546770508</v>
+        <v>0.1704663212435233</v>
       </c>
       <c r="H4">
-        <v>0.09815457546770508</v>
+        <v>0.1704663212435233</v>
       </c>
       <c r="I4">
-        <v>0.05730974350292051</v>
+        <v>0.1796200345423143</v>
       </c>
       <c r="J4">
-        <v>0.04281609607410767</v>
+        <v>0.1563179760070952</v>
       </c>
       <c r="K4">
-        <v>29.4</v>
+        <v>9.65</v>
       </c>
       <c r="L4">
-        <v>0.01244391771776856</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>16.602</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.1766170212765958</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>1.720414507772021</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>16.6</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.1765957446808511</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>1.72020725388601</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.001999999999998892</v>
+      </c>
+      <c r="T4">
+        <v>0.000120467413564564</v>
       </c>
       <c r="U4">
-        <v>463.4</v>
+        <v>56.8</v>
       </c>
       <c r="V4">
-        <v>0.09060514224264346</v>
+        <v>0.6042553191489362</v>
       </c>
       <c r="W4">
-        <v>0.01983939537080774</v>
+        <v>0.08845096241979836</v>
       </c>
       <c r="X4">
-        <v>0.1010043684688603</v>
+        <v>0.08476757902921384</v>
       </c>
       <c r="Y4">
-        <v>-0.08116497309805258</v>
+        <v>0.003683383390584521</v>
       </c>
       <c r="Z4">
-        <v>2.252906006541495</v>
+        <v>1.054644808743169</v>
       </c>
       <c r="AA4">
-        <v>0.09646064002201489</v>
+        <v>0.1648599419091223</v>
       </c>
       <c r="AB4">
-        <v>0.09757830178886145</v>
+        <v>0.08476757902921384</v>
       </c>
       <c r="AC4">
-        <v>-0.001117661766846564</v>
+        <v>0.08009236287990842</v>
       </c>
       <c r="AD4">
-        <v>630.4</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>630.4</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>167</v>
+        <v>-56.8</v>
       </c>
       <c r="AH4">
-        <v>0.109732110219499</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.287420781470843</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.03161980497964594</v>
+        <v>-1.526881720430107</v>
       </c>
       <c r="AK4">
-        <v>0.09653737210243366</v>
+        <v>-1.042201834862385</v>
       </c>
       <c r="AL4">
-        <v>104.2</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>104.2</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>3.818291944276196</v>
-      </c>
-      <c r="AO4">
-        <v>1.299424184261037</v>
+        <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.011508176862508</v>
-      </c>
-      <c r="AQ4">
-        <v>1.299424184261037</v>
+        <v>-5.117117117117117</v>
       </c>
     </row>
     <row r="5">
@@ -981,25 +981,28 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.025</v>
+        <v>0.117</v>
+      </c>
+      <c r="E5">
+        <v>0.229</v>
       </c>
       <c r="G5">
-        <v>0.07807807807807808</v>
+        <v>-0.05389380530973451</v>
       </c>
       <c r="H5">
-        <v>0.07807807807807808</v>
+        <v>-0.05389380530973451</v>
       </c>
       <c r="I5">
-        <v>0.02087087087087087</v>
+        <v>0.07274336283185839</v>
       </c>
       <c r="J5">
-        <v>0.01043543543543544</v>
+        <v>0.07274336283185839</v>
       </c>
       <c r="K5">
-        <v>0.076</v>
+        <v>0.795</v>
       </c>
       <c r="L5">
-        <v>0.01141141141141141</v>
+        <v>0.07035398230088495</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1023,73 +1026,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1.57</v>
+        <v>9.94</v>
       </c>
       <c r="V5">
-        <v>0.1623578076525336</v>
+        <v>0.7049645390070922</v>
       </c>
       <c r="W5">
-        <v>0.008520179372197309</v>
+        <v>0.09375</v>
       </c>
       <c r="X5">
-        <v>0.09536763899564042</v>
+        <v>0.0847853792406677</v>
       </c>
       <c r="Y5">
-        <v>-0.08684745962344312</v>
+        <v>0.008964620759332298</v>
       </c>
       <c r="Z5">
-        <v>1.130154420498897</v>
+        <v>1.622863708171765</v>
       </c>
       <c r="AA5">
-        <v>0.01179365348718819</v>
+        <v>0.1180525635501939</v>
       </c>
       <c r="AB5">
-        <v>0.09522817334484002</v>
+        <v>0.08477205262689989</v>
       </c>
       <c r="AC5">
-        <v>-0.08343451985765182</v>
+        <v>0.03328051092329397</v>
       </c>
       <c r="AD5">
-        <v>0.053</v>
+        <v>0.007</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.053</v>
+        <v>0.007</v>
       </c>
       <c r="AG5">
-        <v>-1.517</v>
+        <v>-9.933</v>
       </c>
       <c r="AH5">
-        <v>0.005450992492029208</v>
+        <v>0.0004962075565322181</v>
       </c>
       <c r="AI5">
-        <v>0.006211180124223601</v>
+        <v>0.0003865908212293587</v>
       </c>
       <c r="AJ5">
-        <v>-0.1860664785968355</v>
+        <v>-2.383729301655868</v>
       </c>
       <c r="AK5">
-        <v>-0.2178658624156255</v>
+        <v>-1.216236071997061</v>
       </c>
       <c r="AL5">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="AM5">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="AN5">
-        <v>0.2226890756302521</v>
+        <v>0.007954545454545455</v>
       </c>
       <c r="AO5">
-        <v>7.722222222222223</v>
+        <v>164.4</v>
       </c>
       <c r="AP5">
-        <v>-6.373949579831933</v>
+        <v>-11.2875</v>
       </c>
       <c r="AQ5">
-        <v>7.722222222222223</v>
+        <v>164.4</v>
       </c>
     </row>
     <row r="6">
@@ -1109,25 +1112,25 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.06370000000000001</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="G6">
-        <v>0.06</v>
+        <v>-0.2434599156118143</v>
       </c>
       <c r="H6">
-        <v>0.06</v>
+        <v>-0.2434599156118143</v>
       </c>
       <c r="I6">
-        <v>-0.3810126582278481</v>
+        <v>-0.04472573839662448</v>
       </c>
       <c r="J6">
-        <v>-0.3810126582278481</v>
+        <v>-0.04472573839662448</v>
       </c>
       <c r="K6">
-        <v>-5.49</v>
+        <v>-0.9</v>
       </c>
       <c r="L6">
-        <v>-0.3474683544303798</v>
+        <v>-0.0379746835443038</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1151,55 +1154,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1.54</v>
+        <v>2.12</v>
       </c>
       <c r="V6">
-        <v>0.02558139534883721</v>
+        <v>0.07285223367697595</v>
       </c>
       <c r="W6">
-        <v>-0.1609970674486804</v>
+        <v>-0.03422053231939164</v>
       </c>
       <c r="X6">
-        <v>0.09551396171681606</v>
+        <v>0.08516801824859205</v>
       </c>
       <c r="Y6">
-        <v>-0.2565110291654964</v>
+        <v>-0.1193885505679837</v>
       </c>
       <c r="Z6">
-        <v>0.4857204340742107</v>
+        <v>0.9377225607343515</v>
       </c>
       <c r="AA6">
-        <v>-0.1850656337421992</v>
+        <v>-0.04194033394001741</v>
       </c>
       <c r="AB6">
-        <v>0.095296119222295</v>
+        <v>0.08486715635088463</v>
       </c>
       <c r="AC6">
-        <v>-0.2803617529644942</v>
+        <v>-0.126807490290902</v>
       </c>
       <c r="AD6">
-        <v>0.514</v>
+        <v>0.325</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.514</v>
+        <v>0.325</v>
       </c>
       <c r="AG6">
-        <v>-1.026</v>
+        <v>-1.795</v>
       </c>
       <c r="AH6">
-        <v>0.008465922192575023</v>
+        <v>0.01104502973661852</v>
       </c>
       <c r="AI6">
-        <v>0.01916909077347654</v>
+        <v>0.01273261508325172</v>
       </c>
       <c r="AJ6">
-        <v>-0.01733869604894041</v>
+        <v>-0.06573887566379785</v>
       </c>
       <c r="AK6">
-        <v>-0.04059507794571496</v>
+        <v>-0.07669301431318096</v>
       </c>
       <c r="AL6">
         <v>0.032</v>
@@ -1208,16 +1211,16 @@
         <v>0.032</v>
       </c>
       <c r="AN6">
-        <v>-0.08667790893760541</v>
+        <v>-0.3392484342379958</v>
       </c>
       <c r="AO6">
-        <v>-188.125</v>
+        <v>-33.125</v>
       </c>
       <c r="AP6">
-        <v>0.1730185497470489</v>
+        <v>1.873695198329854</v>
       </c>
       <c r="AQ6">
-        <v>-188.125</v>
+        <v>-33.125</v>
       </c>
     </row>
   </sheetData>
